--- a/saldo_estoque_exportado.xlsx
+++ b/saldo_estoque_exportado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,426 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Argamassa Pronta 20kg</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Alvenaria e Vedação</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>34</v>
-      </c>
-      <c r="E2" t="n">
-        <v>15.43</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Borracha liquida </t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Alvenaria e Vedação</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>45</v>
-      </c>
-      <c r="E3" t="n">
-        <v>179.99</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cabo 2,5mm </t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Elétrico</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" t="n">
-        <v>119.9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Capacete de Proteção</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Equipamentos de Proteção e Apoio</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>19</v>
-      </c>
-      <c r="E5" t="n">
-        <v>75.90000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>20</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Chapas Aço 50x50 Lisa</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Metálicos e Estruturais Secundários</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>534</v>
-      </c>
-      <c r="E6" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cimento</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Estrutural</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3222</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Concreto usinado 30kg</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Estrutural</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>529</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>15</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Conector de Emenda</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Elétrico</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>390</v>
-      </c>
-      <c r="E9" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Fechadura Cromada</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ferramentas e Fixadores</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>120</v>
-      </c>
-      <c r="E10" t="n">
-        <v>39.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Luva de segurança Volk</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Equipamentos de Proteção e Apoio</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>38</v>
-      </c>
-      <c r="E11" t="n">
-        <v>20.11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MDF branco 185x275</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Madeira e Deriavados</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>450</v>
-      </c>
-      <c r="E12" t="n">
-        <v>239.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Manta de Lã de Vidro Aluminizada 1,2M x 2mm x 50M</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Materiais de Impermeabilização e Isolamento</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>65</v>
-      </c>
-      <c r="E13" t="n">
-        <v>496.22</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Parafuso 3,5x40 Chata</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ferramentas e Fixadores</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>60</v>
-      </c>
-      <c r="E14" t="n">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Rejuner Weber Branco</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Acabamento</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>468</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.41</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Seixos 5Kg</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Acabamento</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>543</v>
-      </c>
-      <c r="E16" t="n">
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Tubo de PVC 100mm x 3 Metros</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Hidráulicos e Saneamento</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2625</v>
-      </c>
-      <c r="E17" t="n">
-        <v>28.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Valvula Alternadora </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Hidráulicos e Saneamento</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18" t="n">
-        <v>109.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Vergalhão 25mm 12 metros</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Estrutural</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>355</v>
-      </c>
-      <c r="E19" t="n">
-        <v>439.9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Vergalhão 4,2mm 12 metros</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Alvenaria e Vedação</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Verniz Brilhante 3,6L</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Acabamento</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>45</v>
-      </c>
-      <c r="E21" t="n">
-        <v>145</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
